--- a/update-ml-labreport-laboratoryobservation/ig/FRSectionLaboratorySupportingInformationLMCDAFHIR.xlsx
+++ b/update-ml-labreport-laboratoryobservation/ig/FRSectionLaboratorySupportingInformationLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:28:49+00:00</t>
+    <t>2026-09-16T13:00:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMLaboratorySupportingInformation vers la section CDA FRCDASectionInformationsCliniques, puis vers FRServiceRequestDocument.supportingInformation (référencé depuis Composition.basedOn).</t>
+    <t>Mapping des éléments du modèle métier FRLMSupportingInformation (partagé avec le mapping imagerie) vers FRServiceRequestDocument.supportingInfo (référencé depuis Composition.basedOn), pour le contexte biologie.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -106,100 +106,70 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMLaboratorySupportingInformation|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSupportingInformation|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-section-informations-cliniques</t>
-  </si>
-  <si>
-    <t>FRLMLaboratorySupportingInformation</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-document|0.1.0</t>
+  </si>
+  <si>
+    <t>FRLMSupportingInformation</t>
   </si>
   <si>
     <t>equivalent</t>
   </si>
   <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>FRCDASectionInformationsCliniques</t>
-  </si>
-  <si>
-    <t>FRLMLaboratorySupportingInformation.codeSection</t>
-  </si>
-  <si>
-    <t>Section.code</t>
-  </si>
-  <si>
-    <t>FRLMLaboratorySupportingInformation.titleSection</t>
-  </si>
-  <si>
-    <t>Section.title</t>
-  </si>
-  <si>
-    <t>FRLMLaboratorySupportingInformation.description</t>
-  </si>
-  <si>
-    <t>Section.text</t>
-  </si>
-  <si>
-    <t>FRLMLaboratorySupportingInformation.entry.observation</t>
-  </si>
-  <si>
-    <t>Section.entry.observation</t>
-  </si>
-  <si>
-    <t>FRCDASimpleObservation</t>
-  </si>
-  <si>
-    <t>FRLMLaboratorySupportingInformation.entry.condition</t>
-  </si>
-  <si>
-    <t>FRCDAProbleme</t>
-  </si>
-  <si>
-    <t>FRLMLaboratorySupportingInformation.entry.medicationAdministration</t>
-  </si>
-  <si>
-    <t>Section.entry.substanceAdministration</t>
-  </si>
-  <si>
-    <t>FRCDATraitement</t>
-  </si>
-  <si>
-    <t>FRLMLaboratorySupportingInformation.entry.vaccination</t>
-  </si>
-  <si>
-    <t>FRCDAVaccination</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-document|0.1.0</t>
-  </si>
-  <si>
-    <t>Composition.basedOn.serviceRequest.supportingInformation</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.supportingInformation</t>
+    <t>Composition.basedOn.serviceRequest.supportingInfo</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument.supportingInfo</t>
+  </si>
+  <si>
+    <t>FRLMSupportingInformation.entry.observation</t>
+  </si>
+  <si>
+    <t>ServiceRequest.supportingInfo</t>
+  </si>
+  <si>
+    <t>Observation</t>
+  </si>
+  <si>
+    <t>FRLMSupportingInformation.entry.condition</t>
+  </si>
+  <si>
+    <t>FRConditionDocument</t>
+  </si>
+  <si>
+    <t>FRLMSupportingInformation.entry.medicationAdministration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration</t>
   </si>
   <si>
     <t>ServiceRequest.supportingInformation</t>
   </si>
   <si>
-    <t>Observation</t>
-  </si>
-  <si>
-    <t>FRConditionDocument</t>
-  </si>
-  <si>
     <t>FRMedicationAdministrationDocument</t>
   </si>
   <si>
+    <t>FRLMSupportingInformation.entry.vaccination</t>
+  </si>
+  <si>
+    <t>FRLMImmunisation</t>
+  </si>
+  <si>
     <t>FRImmunizationDocument</t>
   </si>
   <si>
-    <t>FRLMLaboratorySupportingInformation.entry.otherSupportingInformation</t>
+    <t>FRLMSupportingInformation.entry.otherSupportingInformation</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>Reference(Resource)</t>
   </si>
 </sst>
 </file>
@@ -455,7 +425,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -485,125 +455,9 @@
       <c r="C2" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="D2" t="s" s="2">
-        <v>32</v>
-      </c>
+      <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
         <v>31</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +498,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -659,84 +513,92 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>43</v>
+      </c>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>47</v>
+      </c>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>50</v>
+      </c>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
